--- a/backend python/Tema04 - Base de datos/Clase10_09-30-2026/02.BibliotecaBD.xlsx
+++ b/backend python/Tema04 - Base de datos/Clase10_09-30-2026/02.BibliotecaBD.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jhonathan\Documentos\Cursos\CODIGO\Python Online G30\Sesiones\Tema04 - Base de datos\Clase10_09-30-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/49ff2d670b27dd99/AAA PC JYG OneDrive/Documentos JYG/Cursos JYG/WebFullstackPythonAI tecsup2025/1 frontend foundation webfullstack/backend python/Tema04 - Base de datos/Clase10_09-30-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D67BEF-B825-415E-BD3A-9C0ED6E84050}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{B3D67BEF-B825-415E-BD3A-9C0ED6E84050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E82D3E12-C394-4EE9-B279-D2A7D27D0F83}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="18760" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="editoriales" sheetId="2" r:id="rId1"/>
-    <sheet name="generos" sheetId="3" r:id="rId2"/>
-    <sheet name="paises" sheetId="5" r:id="rId3"/>
-    <sheet name="autores" sheetId="4" r:id="rId4"/>
-    <sheet name="libros" sheetId="1" r:id="rId5"/>
+    <sheet name="libros" sheetId="1" r:id="rId1"/>
+    <sheet name="editoriales" sheetId="2" r:id="rId2"/>
+    <sheet name="generos" sheetId="3" r:id="rId3"/>
+    <sheet name="paises" sheetId="5" r:id="rId4"/>
+    <sheet name="autores" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -504,32 +504,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02BF270-AD2C-4C04-991F-39EA5BD23DED}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <v>987456</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>2020</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>12</v>
+      <c r="B3">
+        <v>456456</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>2021</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>321456</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>2021</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -538,56 +622,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA12E28-BA0C-4D38-B7C9-6CABEC7861B2}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02BF270-AD2C-4C04-991F-39EA5BD23DED}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -596,11 +656,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED7ED66-B854-40FB-8576-EF84108CB902}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA12E28-BA0C-4D38-B7C9-6CABEC7861B2}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -608,44 +668,44 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -654,14 +714,72 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED7ED66-B854-40FB-8576-EF84108CB902}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7AEB62-5674-4921-AA4E-6473C28F614D}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -681,7 +799,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -701,7 +819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -721,7 +839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -741,7 +859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -765,122 +883,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>987456</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>2020</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>456456</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>2021</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>321456</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>2021</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>